--- a/data_kalenderkui.xlsx
+++ b/data_kalenderkui.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/384a2e2a33609d7f/ドキュメント/kalender/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE51C31B-11E3-49B7-874A-1390F46364F6}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="345" windowWidth="20460" windowHeight="10455" tabRatio="883" firstSheet="253" activeTab="257"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="69" activeTab="71" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PT.MAYA AGRO INVESTAMA (1)" sheetId="1" r:id="rId1"/>
@@ -266,17 +272,17 @@
     <sheet name="PT.BINTANG HARAPAN DESA (5)" sheetId="271" r:id="rId257"/>
     <sheet name="PT.SUMATERAJAYA AGROLESTARI" sheetId="272" r:id="rId258"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Zara Rizer</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -305,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8607" uniqueCount="3127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8609" uniqueCount="3128">
   <si>
     <t>MASA BERLAKU</t>
   </si>
@@ -9434,9 +9440,6 @@
     <t>KEC. KENDAWANGAN</t>
   </si>
   <si>
-    <t>DESA NUSAPATI</t>
-  </si>
-  <si>
     <t>DESA SERET AYON</t>
   </si>
   <si>
@@ -9690,12 +9693,18 @@
   </si>
   <si>
     <t>PIPA AIR (BOILER NO.2)</t>
+  </si>
+  <si>
+    <t>SEI.REPIN ESTATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DESA NUSAPATI, KEC.SUNGAI PINYUH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -10293,7 +10302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10490,9 +10499,6 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10698,7 +10704,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10714,9 +10720,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -10754,7 +10760,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -10826,7 +10832,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -10999,7 +11005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11022,16 +11028,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>3044</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="A1" s="72" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -11516,7 +11522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11527,16 +11533,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -11987,7 +11993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6300-000000000000}">
   <sheetPr codeName="Sheet100"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11998,16 +12004,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2973</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -12040,7 +12046,7 @@
 </file>
 
 <file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6400-000000000000}">
   <sheetPr codeName="Sheet101"/>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12054,14 +12060,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -12095,7 +12101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6500-000000000000}">
   <sheetPr codeName="Sheet102"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12106,16 +12112,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3046</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3045</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -12148,7 +12154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6600-000000000000}">
   <sheetPr codeName="Sheet103"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12159,16 +12165,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3069</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -12186,7 +12192,7 @@
         <v>43417</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C4" s="12">
         <v>43052</v>
@@ -12201,7 +12207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6700-000000000000}">
   <sheetPr codeName="Sheet104"/>
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12215,14 +12221,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -12299,7 +12305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6800-000000000000}">
   <sheetPr codeName="Sheet105"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12310,14 +12316,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -12526,7 +12532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6900-000000000000}">
   <sheetPr codeName="Sheet106"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12540,14 +12546,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -12745,7 +12751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6A00-000000000000}">
   <sheetPr codeName="Sheet107"/>
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12756,14 +12762,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -12840,7 +12846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6B00-000000000000}">
   <sheetPr codeName="Sheet108"/>
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12851,16 +12857,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2959</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -12992,7 +12998,7 @@
 </file>
 
 <file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6C00-000000000000}">
   <sheetPr codeName="Sheet109"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13003,16 +13009,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2976</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -13045,7 +13051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13056,16 +13062,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2801</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -13318,7 +13324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet110.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6D00-000000000000}">
   <sheetPr codeName="Sheet110"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13329,16 +13335,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3043</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3042</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -13525,7 +13531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6E00-000000000000}">
   <sheetPr codeName="Sheet111"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13547,16 +13553,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2974</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -13589,7 +13595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6F00-000000000000}">
   <sheetPr codeName="Sheet112"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13600,16 +13606,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2272</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -13642,7 +13648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet113.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7000-000000000000}">
   <sheetPr codeName="Sheet113"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13653,16 +13659,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2271</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -13882,7 +13888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet114.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7100-000000000000}">
   <sheetPr codeName="Sheet114"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13893,14 +13899,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="129"/>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="129"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
+      <c r="A2" s="128"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -13933,7 +13939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet115.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7200-000000000000}">
   <sheetPr codeName="Sheet115"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13944,14 +13950,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="129"/>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="129"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
+      <c r="A2" s="128"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -14204,7 +14210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet116.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7300-000000000000}">
   <sheetPr codeName="Sheet116"/>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14218,16 +14224,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3041</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -14261,7 +14267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet117.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7400-000000000000}">
   <sheetPr codeName="Sheet117"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14272,16 +14278,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3093</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -14314,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet118.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7500-000000000000}">
   <sheetPr codeName="Sheet118"/>
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14325,16 +14331,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>3016</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -14675,7 +14681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet119.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7600-000000000000}">
   <sheetPr codeName="Sheet119"/>
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14692,19 +14698,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2246</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
       <c r="E1" t="s">
         <v>2937</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -14891,7 +14897,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14902,16 +14908,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2801</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="44" t="s">
@@ -15186,7 +15192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet120.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7700-000000000000}">
   <sheetPr codeName="Sheet120"/>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15197,16 +15203,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2246</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -15316,7 +15322,7 @@
 </file>
 
 <file path=xl/worksheets/sheet121.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7800-000000000000}">
   <sheetPr codeName="Sheet121"/>
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15378,18 +15384,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>3048</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="A1" s="72" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
       <c r="F1" s="1"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
       <c r="F2" s="1"/>
       <c r="I2" s="1"/>
     </row>
@@ -15734,7 +15740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet122.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7900-000000000000}">
   <sheetPr codeName="Sheet122"/>
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15745,14 +15751,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -15917,7 +15923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet123.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7A00-000000000000}">
   <sheetPr codeName="Sheet123"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15928,14 +15934,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73"/>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -16210,7 +16216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet124.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7B00-000000000000}">
   <sheetPr codeName="Sheet124"/>
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16221,14 +16227,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -16657,7 +16663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7C00-000000000000}">
   <sheetPr codeName="Sheet125"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16668,16 +16674,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="A1" s="72" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -17062,7 +17068,7 @@
 </file>
 
 <file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7D00-000000000000}">
   <sheetPr codeName="Sheet126"/>
   <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17073,16 +17079,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1517</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -17489,7 +17495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7E00-000000000000}">
   <sheetPr codeName="Sheet127"/>
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17500,14 +17506,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -17826,7 +17832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-7F00-000000000000}">
   <sheetPr codeName="Sheet128"/>
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17837,14 +17843,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -18086,7 +18092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8000-000000000000}">
   <sheetPr codeName="Sheet129"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18097,16 +18103,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="129" t="s">
         <v>1815</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="130"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -18315,7 +18321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18326,16 +18332,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>3030</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="92"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="91"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="93"/>
+      <c r="A2" s="82"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="92"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -18830,7 +18836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8100-000000000000}">
   <sheetPr codeName="Sheet130"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18841,16 +18847,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1884</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -19158,7 +19164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet131.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8200-000000000000}">
   <sheetPr codeName="Sheet131"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19169,16 +19175,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1517</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -19482,7 +19488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8300-000000000000}">
   <sheetPr codeName="Sheet132"/>
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19493,14 +19499,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1884</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -19797,7 +19803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet133.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8400-000000000000}">
   <sheetPr codeName="Sheet133"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19808,16 +19814,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1517</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -20092,7 +20098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet134.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8500-000000000000}">
   <sheetPr codeName="Sheet134"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20103,16 +20109,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2553</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -20321,7 +20327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet135.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8600-000000000000}">
   <sheetPr codeName="Sheet135"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20332,16 +20338,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1884</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -20550,7 +20556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet136.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8700-000000000000}">
   <sheetPr codeName="Sheet136"/>
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20561,16 +20567,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3049</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -20922,7 +20928,7 @@
 </file>
 
 <file path=xl/worksheets/sheet137.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8800-000000000000}">
   <sheetPr codeName="Sheet137"/>
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20972,15 +20978,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
       <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
       <c r="D2" s="56"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -21267,7 +21273,7 @@
 </file>
 
 <file path=xl/worksheets/sheet138.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8900-000000000000}">
   <sheetPr codeName="Sheet138"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21278,16 +21284,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2962</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -21573,7 +21579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet139.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8A00-000000000000}">
   <sheetPr codeName="Sheet139"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21584,16 +21590,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>693</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
@@ -21780,7 +21786,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21791,16 +21797,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>800</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -21899,7 +21905,7 @@
 </file>
 
 <file path=xl/worksheets/sheet140.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8B00-000000000000}">
   <sheetPr codeName="Sheet140"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21910,14 +21916,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -22170,7 +22176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet141.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8C00-000000000000}">
   <sheetPr codeName="Sheet141"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22181,14 +22187,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -22221,7 +22227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet142.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8D00-000000000000}">
   <sheetPr codeName="Sheet142"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22232,16 +22238,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2960</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -22604,7 +22610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet143.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8E00-000000000000}">
   <sheetPr codeName="Sheet143"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22615,14 +22621,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -22886,7 +22892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet144.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8F00-000000000000}">
   <sheetPr codeName="Sheet144"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22897,14 +22903,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
@@ -23102,7 +23108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet145.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9000-000000000000}">
   <sheetPr codeName="Sheet145"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23113,14 +23119,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -23351,7 +23357,7 @@
 </file>
 
 <file path=xl/worksheets/sheet146.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9100-000000000000}">
   <sheetPr codeName="Sheet146"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23362,16 +23368,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>3040</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -23603,7 +23609,7 @@
 </file>
 
 <file path=xl/worksheets/sheet147.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9200-000000000000}">
   <sheetPr codeName="Sheet147"/>
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23614,16 +23620,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2961</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -23942,7 +23948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet148.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9300-000000000000}">
   <sheetPr codeName="Sheet148"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23953,16 +23959,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2164</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -24347,7 +24353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet149.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9400-000000000000}">
   <sheetPr codeName="Sheet149"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24358,16 +24364,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>693</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="131"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="130"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="93"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="92"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -24554,7 +24560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24565,16 +24571,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -25025,7 +25031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet150.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9500-000000000000}">
   <sheetPr codeName="Sheet150"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25036,16 +25042,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>693</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="131"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="130"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="93"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="92"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -25100,7 +25106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet151.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9600-000000000000}">
   <sheetPr codeName="Sheet151"/>
   <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25147,18 +25153,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
       <c r="K1" s="12"/>
       <c r="Q1" s="16"/>
       <c r="R1" s="16"/>
       <c r="S1" s="16"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -25543,7 +25549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet152.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9700-000000000000}">
   <sheetPr codeName="Sheet152"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25554,14 +25560,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -25847,7 +25853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet153.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9800-000000000000}">
   <sheetPr codeName="Sheet153"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25858,16 +25864,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>2963</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -26087,7 +26093,7 @@
 </file>
 
 <file path=xl/worksheets/sheet154.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9900-000000000000}">
   <sheetPr codeName="Sheet154"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26098,16 +26104,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3094</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -26415,7 +26421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet155.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9A00-000000000000}">
   <sheetPr codeName="Sheet155"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26426,16 +26432,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3095</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -26666,7 +26672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet156.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9B00-000000000000}">
   <sheetPr codeName="Sheet156"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26677,14 +26683,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -26970,7 +26976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet157.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9C00-000000000000}">
   <sheetPr codeName="Sheet157"/>
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -26981,14 +26987,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -27329,7 +27335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet158.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9D00-000000000000}">
   <sheetPr codeName="Sheet158"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27340,14 +27346,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -27578,7 +27584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet159.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9E00-000000000000}">
   <sheetPr codeName="Sheet159"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27589,14 +27595,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -27629,7 +27635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27640,16 +27646,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>967</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -27913,7 +27919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet160.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-9F00-000000000000}">
   <sheetPr codeName="Sheet160"/>
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27924,14 +27930,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -28360,7 +28366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet161.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A000-000000000000}">
   <sheetPr codeName="Sheet161"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28371,16 +28377,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2078</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -28666,7 +28672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet162.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A100-000000000000}">
   <sheetPr codeName="Sheet162"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28677,16 +28683,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2079</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -28972,7 +28978,7 @@
 </file>
 
 <file path=xl/worksheets/sheet163.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A200-000000000000}">
   <sheetPr codeName="Sheet163"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28983,16 +28989,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2963</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -29290,7 +29296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet164.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A300-000000000000}">
   <sheetPr codeName="Sheet164"/>
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -29301,14 +29307,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -29396,7 +29402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet165.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A400-000000000000}">
   <sheetPr codeName="Sheet165"/>
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -29410,16 +29416,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1050</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -29551,7 +29557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet166.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A500-000000000000}">
   <sheetPr codeName="Sheet166"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -29562,14 +29568,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
@@ -29690,7 +29696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet167.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A600-000000000000}">
   <sheetPr codeName="Sheet167"/>
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -29731,15 +29737,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
       <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -30169,7 +30175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet168.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A700-000000000000}">
   <sheetPr codeName="Sheet168"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -30180,16 +30186,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>879</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -30552,7 +30558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet169.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A800-000000000000}">
   <sheetPr codeName="Sheet169"/>
   <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -30563,16 +30569,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>879</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
@@ -30962,7 +30968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -30972,16 +30978,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2671</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -31531,7 +31537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet170.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-A900-000000000000}">
   <sheetPr codeName="Sheet170"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -31542,16 +31548,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>1275</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -31936,7 +31942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet171.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-AA00-000000000000}">
   <sheetPr codeName="Sheet171"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -31947,16 +31953,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>1275</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -32341,7 +32347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet172.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-AB00-000000000000}">
   <sheetPr codeName="Sheet172"/>
   <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -32352,16 +32358,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>1511</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -32867,7 +32873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet173.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-AC00-000000000000}">
   <sheetPr codeName="Sheet173"/>
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -32878,16 +32884,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>879</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -33283,7 +33289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet174.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-AD00-000000000000}">
   <sheetPr codeName="Sheet174"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33294,16 +33300,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>1891</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -33688,7 +33694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet175.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-AE00-000000000000}">
   <sheetPr codeName="Sheet175"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33699,16 +33705,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2128</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -34093,7 +34099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet176.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-AF00-000000000000}">
   <sheetPr codeName="Sheet176"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34104,16 +34110,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2129</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -34498,7 +34504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet177.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B000-000000000000}">
   <sheetPr codeName="Sheet177"/>
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34509,16 +34515,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="93" t="s">
         <v>2128</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="59" t="s">
@@ -34903,7 +34909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet178.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B100-000000000000}">
   <sheetPr codeName="Sheet178"/>
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34923,15 +34929,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -35272,7 +35278,7 @@
 </file>
 
 <file path=xl/worksheets/sheet179.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B200-000000000000}">
   <sheetPr codeName="Sheet179"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35283,14 +35289,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -35521,7 +35527,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35532,14 +35538,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -35902,7 +35908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet180.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B300-000000000000}">
   <sheetPr codeName="Sheet180"/>
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -35913,16 +35919,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1961</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -36252,7 +36258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet181.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B400-000000000000}">
   <sheetPr codeName="Sheet181"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -36263,16 +36269,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>563</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -36582,7 +36588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet182.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B500-000000000000}">
   <sheetPr codeName="Sheet182"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -36593,16 +36599,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1075</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -36668,7 +36674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet183.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B600-000000000000}">
   <sheetPr codeName="Sheet183"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -36679,16 +36685,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2964</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -36721,7 +36727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet184.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B700-000000000000}">
   <sheetPr codeName="Sheet184"/>
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -36732,14 +36738,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -36904,7 +36910,7 @@
 </file>
 
 <file path=xl/worksheets/sheet185.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B800-000000000000}">
   <sheetPr codeName="Sheet185"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -36915,16 +36921,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2965</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -36957,7 +36963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet186.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-B900-000000000000}">
   <sheetPr codeName="Sheet186"/>
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -36968,16 +36974,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
-        <v>3042</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -37065,7 +37071,7 @@
 </file>
 
 <file path=xl/worksheets/sheet187.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-BA00-000000000000}">
   <sheetPr codeName="Sheet187"/>
   <dimension ref="A1:AF27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37106,19 +37112,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2966</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
       <c r="AF1" t="s">
         <v>2483</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -37404,7 +37410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet188.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-BB00-000000000000}">
   <sheetPr codeName="Sheet188"/>
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37415,14 +37421,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -37719,7 +37725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet189.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-BC00-000000000000}">
   <sheetPr codeName="Sheet189"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37730,14 +37736,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -37781,7 +37787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37792,14 +37798,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -37942,7 +37948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet190.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-BD00-000000000000}">
   <sheetPr codeName="Sheet190"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37953,14 +37959,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -37993,7 +37999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet191.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-BE00-000000000000}">
   <sheetPr codeName="Sheet191"/>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38004,14 +38010,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -38104,7 +38110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet192.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-BF00-000000000000}">
   <sheetPr codeName="Sheet192"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38115,14 +38121,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -38408,7 +38414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet193.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C000-000000000000}">
   <sheetPr codeName="Sheet193"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38419,14 +38425,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -38492,7 +38498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet194.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C100-000000000000}">
   <sheetPr codeName="Sheet194"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38503,16 +38509,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>2456</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -38820,7 +38826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet195.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C200-000000000000}">
   <sheetPr codeName="Sheet195"/>
   <dimension ref="A2:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39024,7 +39030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet196.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C300-000000000000}">
   <sheetPr codeName="Sheet196"/>
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39035,16 +39041,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3122</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -39374,7 +39380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet197.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C400-000000000000}">
   <sheetPr codeName="Sheet197"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39385,16 +39391,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2492</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="131"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="130"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="93"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="92"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -39669,7 +39675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet198.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C500-000000000000}">
   <sheetPr codeName="Sheet198"/>
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39689,14 +39695,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -39773,7 +39779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet199.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C600-000000000000}">
   <sheetPr codeName="Sheet199"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39784,14 +39790,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -39987,7 +39993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39998,16 +40004,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1438</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -40271,7 +40277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -40282,16 +40288,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2801</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -40412,7 +40418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet200.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C700-000000000000}">
   <sheetPr codeName="Sheet200"/>
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -40423,16 +40429,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2967</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -40806,7 +40812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet201.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C800-000000000000}">
   <sheetPr codeName="Sheet201"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -40817,14 +40823,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -40857,7 +40863,7 @@
 </file>
 
 <file path=xl/worksheets/sheet202.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-C900-000000000000}">
   <sheetPr codeName="Sheet202"/>
   <dimension ref="A1:C100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -40876,14 +40882,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -41972,7 +41978,7 @@
 </file>
 
 <file path=xl/worksheets/sheet203.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-CA00-000000000000}">
   <sheetPr codeName="Sheet203"/>
   <dimension ref="A1:C100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -41983,14 +41989,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="132"/>
-      <c r="B1" s="133"/>
-      <c r="C1" s="134"/>
+      <c r="A1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="133"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="135"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="136"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="135"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -43079,7 +43085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet204.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-CB00-000000000000}">
   <sheetPr codeName="Sheet204"/>
   <dimension ref="A2:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43514,7 +43520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet205.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-CC00-000000000000}">
   <sheetPr codeName="Sheet205"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43525,14 +43531,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -43653,7 +43659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet206.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-CD00-000000000000}">
   <sheetPr codeName="Sheet206"/>
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43664,14 +43670,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -43748,7 +43754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet207.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-CE00-000000000000}">
   <sheetPr codeName="Sheet207"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43759,16 +43765,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2968</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -43801,7 +43807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet208.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-CF00-000000000000}">
   <sheetPr codeName="Sheet208"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43812,14 +43818,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -43885,7 +43891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet209.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D000-000000000000}">
   <sheetPr codeName="Sheet209"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -43899,14 +43905,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -44041,7 +44047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44052,16 +44058,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>967</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="60" t="s">
@@ -44325,7 +44331,7 @@
 </file>
 
 <file path=xl/worksheets/sheet210.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D100-000000000000}">
   <sheetPr codeName="Sheet210"/>
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44336,14 +44342,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -44497,7 +44503,7 @@
 </file>
 
 <file path=xl/worksheets/sheet211.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D200-000000000000}">
   <sheetPr codeName="Sheet211"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44508,16 +44514,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>3029</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -44583,7 +44589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet212.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D300-000000000000}">
   <sheetPr codeName="Sheet212"/>
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44597,16 +44603,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2978</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -44694,7 +44700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet213.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D400-000000000000}">
   <sheetPr codeName="Sheet213"/>
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44705,16 +44711,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2977</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -44846,7 +44852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet214.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D500-000000000000}">
   <sheetPr codeName="Sheet214"/>
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44857,16 +44863,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2969</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -45328,7 +45334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet215.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D600-000000000000}">
   <sheetPr codeName="Sheet215"/>
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -45339,16 +45345,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>3028</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -45425,7 +45431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet216.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D700-000000000000}">
   <sheetPr codeName="Sheet216"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -45439,14 +45445,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -45490,7 +45496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet217.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D800-000000000000}">
   <sheetPr codeName="Sheet217"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -45501,16 +45507,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2291</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -45554,7 +45560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet218.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-D900-000000000000}">
   <sheetPr codeName="Sheet218"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -45568,16 +45574,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1708</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -45610,7 +45616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet219.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-DA00-000000000000}">
   <sheetPr codeName="Sheet219"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -45621,16 +45627,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2254</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -45839,7 +45845,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -45850,14 +45856,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46299,7 +46305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet220.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-DB00-000000000000}">
   <sheetPr codeName="Sheet220"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46310,14 +46316,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -46350,7 +46356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet221.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-DC00-000000000000}">
   <sheetPr codeName="Sheet221"/>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46361,16 +46367,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
-        <v>3121</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -46480,7 +46486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet222.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-DD00-000000000000}">
   <sheetPr codeName="Sheet222"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46494,14 +46500,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46534,7 +46540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet223.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-DE00-000000000000}">
   <sheetPr codeName="Sheet223"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46545,14 +46551,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46585,7 +46591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet224.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-DF00-000000000000}">
   <sheetPr codeName="Sheet224"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46596,14 +46602,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46658,7 +46664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet225.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E000-000000000000}">
   <sheetPr codeName="Sheet225"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46669,14 +46675,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46710,7 +46716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet226.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E100-000000000000}">
   <sheetPr codeName="Sheet226"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46721,14 +46727,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46761,7 +46767,7 @@
 </file>
 
 <file path=xl/worksheets/sheet227.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E200-000000000000}">
   <sheetPr codeName="Sheet227"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46772,14 +46778,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -46823,7 +46829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet228.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E300-000000000000}">
   <sheetPr codeName="Sheet228"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -46837,16 +46843,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3050</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -47055,7 +47061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet229.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E400-000000000000}">
   <sheetPr codeName="Sheet229"/>
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -47066,14 +47072,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -47315,7 +47321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -47326,14 +47332,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -47872,7 +47878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet230.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E500-000000000000}">
   <sheetPr codeName="Sheet230"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -47883,14 +47889,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -47923,7 +47929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet231.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E600-000000000000}">
   <sheetPr codeName="Sheet231"/>
   <dimension ref="A2:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -47973,7 +47979,7 @@
 </file>
 
 <file path=xl/worksheets/sheet232.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E700-000000000000}">
   <sheetPr codeName="Sheet232"/>
   <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48028,17 +48034,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="120" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
       <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -48087,7 +48093,7 @@
 </file>
 
 <file path=xl/worksheets/sheet233.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E800-000000000000}">
   <sheetPr codeName="Sheet233"/>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48098,14 +48104,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -48281,7 +48287,7 @@
 </file>
 
 <file path=xl/worksheets/sheet234.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-E900-000000000000}">
   <sheetPr codeName="Sheet234"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48292,14 +48298,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -48354,7 +48360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet235.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-EA00-000000000000}">
   <sheetPr codeName="Sheet235"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48365,14 +48371,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -48493,7 +48499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet236.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-EB00-000000000000}">
   <sheetPr codeName="Sheet236"/>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48504,16 +48510,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2970</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -48623,7 +48629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet237.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-EC00-000000000000}">
   <sheetPr codeName="Sheet237"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48634,14 +48640,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -48762,7 +48768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet238.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-ED00-000000000000}">
   <sheetPr codeName="Sheet238"/>
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -48773,16 +48779,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2970</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -49024,7 +49030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet239.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-EE00-000000000000}">
   <sheetPr codeName="Sheet239"/>
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -49035,16 +49041,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>935</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -49341,7 +49347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -49352,16 +49358,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>800</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -49460,7 +49466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet240.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-EF00-000000000000}">
   <sheetPr codeName="Sheet240"/>
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -49471,14 +49477,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -49566,7 +49572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet241.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F000-000000000000}">
   <sheetPr codeName="Sheet241"/>
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -49577,14 +49583,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -49914,7 +49920,7 @@
 </file>
 
 <file path=xl/worksheets/sheet242.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F100-000000000000}">
   <sheetPr codeName="Sheet242"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -49925,14 +49931,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
@@ -50119,7 +50125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet243.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F200-000000000000}">
   <sheetPr codeName="Sheet243"/>
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -50130,16 +50136,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>935</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -50436,7 +50442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet244.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F300-000000000000}">
   <sheetPr codeName="Sheet244"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -50447,16 +50453,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2518</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -50654,7 +50660,7 @@
 </file>
 
 <file path=xl/worksheets/sheet245.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F400-000000000000}">
   <sheetPr codeName="Sheet245"/>
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -50665,14 +50671,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="137"/>
-      <c r="B1" s="137"/>
-      <c r="C1" s="138"/>
+      <c r="A1" s="136"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
@@ -51014,7 +51020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet246.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F500-000000000000}">
   <sheetPr codeName="Sheet246"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51025,14 +51031,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
@@ -51395,7 +51401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet247.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F600-000000000000}">
   <sheetPr codeName="Sheet247"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51406,16 +51412,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2979</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -51459,7 +51465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet248.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F700-000000000000}">
   <sheetPr codeName="Sheet248"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51470,16 +51476,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2982</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -51765,7 +51771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet249.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F800-000000000000}">
   <sheetPr codeName="Sheet249"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -51776,16 +51782,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2231</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -52005,7 +52011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52016,16 +52022,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3120</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3119</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -52168,7 +52174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet250.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-F900-000000000000}">
   <sheetPr codeName="Sheet250"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52179,14 +52185,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -52219,7 +52225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet251.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-FA00-000000000000}">
   <sheetPr codeName="Sheet251"/>
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52230,16 +52236,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>935</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -52536,7 +52542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet252.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-FB00-000000000000}">
   <sheetPr codeName="Sheet252"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52547,16 +52553,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2246</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -52820,7 +52826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet253.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-FC00-000000000000}">
   <sheetPr codeName="Sheet253"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52831,16 +52837,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>3031</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -53038,7 +53044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet254.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-FD00-000000000000}">
   <sheetPr codeName="Sheet254"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -53049,16 +53055,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
-        <v>3050</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -53073,233 +53079,233 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>609</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>610</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>611</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>612</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>289</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>613</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>614</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>164</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>224</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>3060</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>3061</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>3062</v>
       </c>
     </row>
   </sheetData>
@@ -53311,7 +53317,7 @@
 </file>
 
 <file path=xl/worksheets/sheet255.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-FE00-000000000000}">
   <sheetPr codeName="Sheet255"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -53322,16 +53328,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3097</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -53349,7 +53355,7 @@
         <v>46657</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="C4" s="12">
         <v>45927</v>
@@ -53364,7 +53370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet256.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-FF00-000000000000}">
   <sheetPr codeName="Sheet256"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -53375,16 +53381,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>800</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="44" t="s">
@@ -53402,7 +53408,7 @@
         <v>46185</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C4" s="12">
         <v>45820</v>
@@ -53413,7 +53419,7 @@
         <v>46185</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="C5" s="4">
         <v>45820</v>
@@ -53424,7 +53430,7 @@
         <v>46185</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="C6" s="12">
         <v>45820</v>
@@ -53435,7 +53441,7 @@
         <v>46185</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C7" s="4">
         <v>45820</v>
@@ -53446,7 +53452,7 @@
         <v>46185</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="C8" s="12">
         <v>45820</v>
@@ -53457,7 +53463,7 @@
         <v>46185</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="C9" s="4">
         <v>45820</v>
@@ -53468,7 +53474,7 @@
         <v>46185</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="C10" s="12">
         <v>45820</v>
@@ -53479,7 +53485,7 @@
         <v>46185</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="C11" s="4">
         <v>45820</v>
@@ -53501,7 +53507,7 @@
         <v>46185</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C13" s="4">
         <v>45820</v>
@@ -53512,7 +53518,7 @@
         <v>46185</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="C14" s="12">
         <v>45820</v>
@@ -53534,7 +53540,7 @@
         <v>46185</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="C16" s="12">
         <v>45820</v>
@@ -53556,7 +53562,7 @@
         <v>46185</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="C18" s="12">
         <v>45820</v>
@@ -53567,7 +53573,7 @@
         <v>46185</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="C19" s="4">
         <v>45820</v>
@@ -53578,7 +53584,7 @@
         <v>46185</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="C20" s="12">
         <v>45820</v>
@@ -53589,7 +53595,7 @@
         <v>46185</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="C21" s="4">
         <v>45820</v>
@@ -53605,7 +53611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet257.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0001-000000000000}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -53615,136 +53621,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>2246</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="71" t="s">
         <v>2021</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3118</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="3" t="s">
         <v>909</v>
       </c>
-      <c r="C5" s="71" t="s">
-        <v>3118</v>
+      <c r="C5" s="3" t="s">
+        <v>3117</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B6" s="71" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>1434</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>3118</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="3" t="s">
         <v>1435</v>
       </c>
-      <c r="C7" s="71" t="s">
-        <v>3118</v>
+      <c r="C7" s="3" t="s">
+        <v>3117</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B8" s="71" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>1436</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>3118</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="3" t="s">
         <v>1437</v>
       </c>
-      <c r="C9" s="71" t="s">
-        <v>3118</v>
+      <c r="C9" s="3" t="s">
+        <v>3117</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B10" s="71" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>592</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>3118</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>3115</v>
-      </c>
-      <c r="C11" s="71" t="s">
-        <v>3118</v>
+      <c r="B11" s="3" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>3117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B12" s="71" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>3116</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>3118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
-        <v>3119</v>
-      </c>
-      <c r="B13" s="71" t="s">
+      <c r="C13" s="3" t="s">
         <v>3117</v>
-      </c>
-      <c r="C13" s="71" t="s">
-        <v>3118</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -53761,7 +53767,7 @@
 </file>
 
 <file path=xl/worksheets/sheet258.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0101-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -53771,16 +53777,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1050</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
@@ -53809,7 +53815,7 @@
         <v>46637</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="C5" s="4">
         <v>45907</v>
@@ -53820,7 +53826,7 @@
         <v>46637</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="C6" s="4">
         <v>45907</v>
@@ -53897,7 +53903,7 @@
         <v>46637</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="C13" s="4">
         <v>45907</v>
@@ -53908,7 +53914,7 @@
         <v>46637</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="C14" s="4">
         <v>45907</v>
@@ -53989,7 +53995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -54000,14 +54006,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -54370,7 +54376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -54381,16 +54387,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2801</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -54731,7 +54737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -54742,14 +54748,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -55112,7 +55118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -55123,14 +55129,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="104"/>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
+      <c r="A1" s="103"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="105"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -55460,7 +55466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -55471,16 +55477,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
-        <v>2937</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="A1" s="84" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
+      <c r="A2" s="82"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -55546,7 +55552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -55557,14 +55563,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -55630,7 +55636,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -55641,14 +55647,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79"/>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -55769,7 +55775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -55780,16 +55786,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3085</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
@@ -55807,7 +55813,7 @@
         <v>46157</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="C4" s="12">
         <v>45792</v>
@@ -55818,7 +55824,7 @@
         <v>46157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="C5" s="4">
         <v>45792</v>
@@ -55829,7 +55835,7 @@
         <v>46157</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="C6" s="12">
         <v>45792</v>
@@ -55840,7 +55846,7 @@
         <v>46157</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="C7" s="4">
         <v>45792</v>
@@ -55851,7 +55857,7 @@
         <v>46157</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="C8" s="12">
         <v>45792</v>
@@ -55862,7 +55868,7 @@
         <v>46157</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="C9" s="4">
         <v>45792</v>
@@ -55873,7 +55879,7 @@
         <v>46157</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="C10" s="12">
         <v>45792</v>
@@ -55884,7 +55890,7 @@
         <v>46157</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="C11" s="4">
         <v>45792</v>
@@ -55906,7 +55912,7 @@
         <v>46157</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="C13" s="4">
         <v>45792</v>
@@ -55917,7 +55923,7 @@
         <v>46157</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="C14" s="12">
         <v>45792</v>
@@ -55928,7 +55934,7 @@
         <v>46157</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="C15" s="4">
         <v>45792</v>
@@ -55939,7 +55945,7 @@
         <v>46157</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="C16" s="12">
         <v>45792</v>
@@ -55950,7 +55956,7 @@
         <v>46157</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="C17" s="4">
         <v>45792</v>
@@ -55961,7 +55967,7 @@
         <v>46157</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="C18" s="12">
         <v>45792</v>
@@ -55972,7 +55978,7 @@
         <v>46157</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="C19" s="4">
         <v>45792</v>
@@ -55987,7 +55993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -56001,14 +56007,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -56088,7 +56094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -56099,16 +56105,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
-        <v>3086</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -56185,7 +56191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -56211,16 +56217,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2951</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="108"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="109"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="111"/>
+      <c r="A2" s="108"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="110"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -56525,7 +56531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -56536,16 +56542,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3087</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -56754,7 +56760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -56765,14 +56771,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="95" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -57102,7 +57110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -57113,14 +57121,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -57538,7 +57546,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -57549,16 +57557,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2231</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
@@ -57734,7 +57742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -57745,16 +57753,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
-        <v>3045</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="A1" s="84" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -57908,7 +57916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <sheetPr codeName="Sheet40"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -57919,14 +57927,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -58146,7 +58154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <sheetPr codeName="Sheet41"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58160,16 +58168,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>3027</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -58389,7 +58397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <sheetPr codeName="Sheet42"/>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58400,14 +58408,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="118"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="120"/>
+      <c r="A2" s="117"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="119"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -58517,7 +58525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <sheetPr codeName="Sheet43"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58534,16 +58542,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="120" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="121"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
+      <c r="A2" s="120"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -58587,7 +58595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <sheetPr codeName="Sheet44"/>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58598,16 +58606,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2952</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -58717,7 +58725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
   <sheetPr codeName="Sheet45"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58728,16 +58736,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2952</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -58751,13 +58759,13 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>1058</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>1057</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -58770,7 +58778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2D00-000000000000}">
   <sheetPr codeName="Sheet46"/>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58784,16 +58792,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3088</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -58969,7 +58977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2E00-000000000000}">
   <sheetPr codeName="Sheet47"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -58980,16 +58988,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3089</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -59022,7 +59030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2F00-000000000000}">
   <sheetPr codeName="Sheet48"/>
   <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -59048,14 +59056,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -59373,7 +59381,7 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3000-000000000000}">
   <sheetPr codeName="Sheet49"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -59384,16 +59392,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2953</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -59536,7 +59544,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:BA36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -59636,17 +59644,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A1" s="86"/>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
+      <c r="A1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
       <c r="BA1" t="s">
         <v>2937</v>
       </c>
     </row>
     <row r="2" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
@@ -60008,7 +60016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3100-000000000000}">
   <sheetPr codeName="Sheet50"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60019,16 +60027,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2953</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -60248,7 +60256,7 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3200-000000000000}">
   <sheetPr codeName="Sheet51"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60259,14 +60267,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="116"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -60321,7 +60329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
   <sheetPr codeName="Sheet52"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60332,16 +60340,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2953</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -60374,7 +60382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3400-000000000000}">
   <sheetPr codeName="Sheet53"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60385,16 +60393,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>2953</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
+      <c r="A2" s="82"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
@@ -60625,7 +60633,7 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3500-000000000000}">
   <sheetPr codeName="Sheet54"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60636,16 +60644,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3090</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3089</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -60689,7 +60697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3600-000000000000}">
   <sheetPr codeName="Sheet55"/>
   <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60721,17 +60729,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2954</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -60767,7 +60775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3700-000000000000}">
   <sheetPr codeName="Sheet56"/>
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -60778,16 +60786,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>3004</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -61018,7 +61026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3800-000000000000}">
   <sheetPr codeName="Sheet57"/>
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -61029,16 +61037,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2955</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
@@ -61335,7 +61343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3900-000000000000}">
   <sheetPr codeName="Sheet58"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -61346,14 +61354,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -61397,7 +61405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3A00-000000000000}">
   <sheetPr codeName="Sheet59"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -61408,16 +61416,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2954</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -61615,7 +61623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -61626,16 +61634,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2908</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="34" t="s">
@@ -61987,7 +61995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3B00-000000000000}">
   <sheetPr codeName="Sheet60"/>
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -61998,16 +62006,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2955</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -62161,7 +62169,7 @@
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3C00-000000000000}">
   <sheetPr codeName="Sheet61"/>
   <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -62172,14 +62180,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -62619,7 +62627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3D00-000000000000}">
   <sheetPr codeName="Sheet62"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -62630,16 +62638,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>3004</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -62705,7 +62713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3E00-000000000000}">
   <sheetPr codeName="Sheet63"/>
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -62743,16 +62751,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>563</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -63039,7 +63047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3F00-000000000000}">
   <sheetPr codeName="Sheet64"/>
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -63050,14 +63058,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1961</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -63387,7 +63395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4000-000000000000}">
   <sheetPr codeName="Sheet65"/>
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -63398,16 +63406,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1961</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -63649,7 +63657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4100-000000000000}">
   <sheetPr codeName="Sheet66"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -63660,14 +63668,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -64030,7 +64038,7 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4200-000000000000}">
   <sheetPr codeName="Sheet67"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -64041,16 +64049,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>1961</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -64325,7 +64333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4300-000000000000}">
   <sheetPr codeName="Sheet68"/>
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -64336,14 +64344,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="96"/>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
+      <c r="A1" s="95"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -64491,7 +64499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4400-000000000000}">
   <sheetPr codeName="Sheet69"/>
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -64502,14 +64510,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -64677,7 +64685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -64688,16 +64696,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2950</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -64840,7 +64848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4500-000000000000}">
   <sheetPr codeName="Sheet70"/>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -64851,14 +64859,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="121"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -65133,7 +65141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4600-000000000000}">
   <sheetPr codeName="Sheet71"/>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -65144,16 +65152,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>563</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -65329,7 +65337,7 @@
 </file>
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4700-000000000000}">
   <sheetPr codeName="Sheet72"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -65346,16 +65354,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>3091</v>
-      </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
@@ -65608,7 +65616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4800-000000000000}">
   <sheetPr codeName="Sheet73"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -65619,16 +65627,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3113</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -65881,7 +65889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4900-000000000000}">
   <sheetPr codeName="Sheet74"/>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -65901,14 +65909,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -66007,7 +66015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4A00-000000000000}">
   <sheetPr codeName="Sheet75"/>
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66018,16 +66026,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2956</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -66192,7 +66200,7 @@
 </file>
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4B00-000000000000}">
   <sheetPr codeName="Sheet76"/>
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66203,14 +66211,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -66474,7 +66482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4C00-000000000000}">
   <sheetPr codeName="Sheet77"/>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66485,16 +66493,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2956</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -66604,7 +66612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4D00-000000000000}">
   <sheetPr codeName="Sheet78"/>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66615,16 +66623,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
-        <v>3065</v>
-      </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -66668,7 +66676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4E00-000000000000}">
   <sheetPr codeName="Sheet79"/>
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66679,16 +66687,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>3064</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="A1" s="72" t="s">
+        <v>3063</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="128"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="93"/>
+      <c r="A2" s="127"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="92"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -66757,7 +66765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -66768,16 +66776,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2801</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="43" t="s">
@@ -66997,7 +67005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4F00-000000000000}">
   <sheetPr codeName="Sheet80"/>
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -67008,16 +67016,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2975</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -67084,7 +67092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5000-000000000000}">
   <sheetPr codeName="Sheet81"/>
   <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -67119,16 +67127,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2972</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -67396,7 +67404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5100-000000000000}">
   <sheetPr codeName="Sheet82"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -67407,16 +67415,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3092</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -67614,7 +67622,7 @@
 </file>
 
 <file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5200-000000000000}">
   <sheetPr codeName="Sheet83"/>
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -67625,16 +67633,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2972</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
@@ -67832,7 +67840,7 @@
 </file>
 
 <file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5300-000000000000}">
   <sheetPr codeName="Sheet84"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -67843,16 +67851,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -68039,7 +68047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5400-000000000000}">
   <sheetPr codeName="Sheet85"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68050,14 +68058,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98"/>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="A1" s="97"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
@@ -68090,7 +68098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5500-000000000000}">
   <sheetPr codeName="Sheet86"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68101,16 +68109,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="101"/>
-      <c r="B2" s="102"/>
-      <c r="C2" s="103"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="102"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -68297,7 +68305,7 @@
 </file>
 
 <file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5600-000000000000}">
   <sheetPr codeName="Sheet87"/>
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68308,16 +68316,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -68471,7 +68479,7 @@
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5700-000000000000}">
   <sheetPr codeName="Sheet88"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68482,16 +68490,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -68799,7 +68807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5800-000000000000}">
   <sheetPr codeName="Sheet89"/>
   <dimension ref="A1:V23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68834,17 +68842,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
       <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
       <c r="V2" s="1"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -69087,7 +69095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -69098,16 +69106,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2801</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="43" t="s">
@@ -69349,7 +69357,7 @@
 </file>
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5900-000000000000}">
   <sheetPr codeName="Sheet90"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -69360,16 +69368,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3067</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -69622,7 +69630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5A00-000000000000}">
   <sheetPr codeName="Sheet91"/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -69633,16 +69641,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
-        <v>3066</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="A1" s="78" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -69862,7 +69870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5B00-000000000000}">
   <sheetPr codeName="Sheet92"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -69873,16 +69881,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2518</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -70025,7 +70033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5C00-000000000000}">
   <sheetPr codeName="Sheet93"/>
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -70036,16 +70044,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>2957</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -70408,7 +70416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5D00-000000000000}">
   <sheetPr codeName="Sheet94"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -70419,14 +70427,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -70613,7 +70621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5E00-000000000000}">
   <sheetPr codeName="Sheet95"/>
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -70624,14 +70632,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="95" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -70818,7 +70828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5F00-000000000000}">
   <sheetPr codeName="Sheet96"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -70829,16 +70839,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="77"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -71091,7 +71101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6000-000000000000}">
   <sheetPr codeName="Sheet97"/>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -71102,14 +71112,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="A1" s="105"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="106"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
+      <c r="A2" s="105"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -71142,7 +71152,7 @@
 </file>
 
 <file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6100-000000000000}">
   <sheetPr codeName="Sheet98"/>
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -71153,16 +71163,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="97" t="s">
         <v>818</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -71217,7 +71227,7 @@
 </file>
 
 <file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-6200-000000000000}">
   <sheetPr codeName="Sheet99"/>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -71231,16 +71241,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>2958</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">

--- a/data_kalenderkui.xlsx
+++ b/data_kalenderkui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/384a2e2a33609d7f/ドキュメント/kalender/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE51C31B-11E3-49B7-874A-1390F46364F6}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1B72FEF-7E80-4061-9261-3D56139F5DAF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="69" activeTab="71" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="92" activeTab="94" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PT.MAYA AGRO INVESTAMA (1)" sheetId="1" r:id="rId1"/>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8609" uniqueCount="3128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="3130">
   <si>
     <t>MASA BERLAKU</t>
   </si>
@@ -9699,6 +9699,12 @@
   </si>
   <si>
     <t xml:space="preserve"> DESA NUSAPATI, KEC.SUNGAI PINYUH</t>
+  </si>
+  <si>
+    <t>MEMPAWAH</t>
+  </si>
+  <si>
+    <t>KEC.LOA KULU, KALTIM</t>
   </si>
 </sst>
 </file>
@@ -10302,7 +10308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10680,21 +10686,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -29307,14 +29298,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="121"/>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
+      <c r="A1" s="78" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -41989,14 +41982,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="131"/>
-      <c r="B1" s="132"/>
-      <c r="C1" s="133"/>
+      <c r="A1" s="78" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="134"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="135"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -50671,9 +50666,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="136"/>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
+      <c r="A1" s="131"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="125"/>

--- a/data_kalenderkui.xlsx
+++ b/data_kalenderkui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/384a2e2a33609d7f/ドキュメント/kalender/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1B72FEF-7E80-4061-9261-3D56139F5DAF}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{269B3EDB-5170-4C21-96E8-AA510EC77D7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="92" activeTab="94" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="62" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PT.MAYA AGRO INVESTAMA (1)" sheetId="1" r:id="rId1"/>
@@ -30995,7 +30995,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
-        <v>46206</v>
+        <v>45841</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>2672</v>
@@ -31006,7 +31006,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>46206</v>
+        <v>45841</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2675</v>
@@ -63056,11 +63056,13 @@
       <c r="A1" s="78" t="s">
         <v>1961</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -63383,7 +63385,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_kalenderkui.xlsx
+++ b/data_kalenderkui.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="21" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{269B3EDB-5170-4C21-96E8-AA510EC77D7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="62" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="62" activeTab="62" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PT.MAYA AGRO INVESTAMA (1)" sheetId="1" r:id="rId1"/>

--- a/data_kalenderkui.xlsx
+++ b/data_kalenderkui.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/384a2e2a33609d7f/ドキュメント/kalender/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{269B3EDB-5170-4C21-96E8-AA510EC77D7E}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13006653-0EEF-49F1-9693-2F77741CBB55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="62" activeTab="62" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="3130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="3131">
   <si>
     <t>MASA BERLAKU</t>
   </si>
@@ -9705,6 +9705,9 @@
   </si>
   <si>
     <t>KEC.LOA KULU, KALTIM</t>
+  </si>
+  <si>
+    <t>KAPUASHULU ESTATE</t>
   </si>
 </sst>
 </file>
@@ -62713,8 +62716,8 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="27.42578125" customWidth="1"/>
@@ -62747,7 +62750,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
-        <v>563</v>
+        <v>3130</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="80"/>

--- a/data_kalenderkui.xlsx
+++ b/data_kalenderkui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/384a2e2a33609d7f/ドキュメント/kalender/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12EA85F7-E852-4F5A-9729-C87727536BF0}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_1CA1E26B38A44CADB4944F086857B88B36FF4A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADDC5FC2-7F1B-4C50-B1BA-544C587C0935}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="62" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="883" firstSheet="61" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PT.MAYA AGRO INVESTAMA (1)" sheetId="1" r:id="rId1"/>
@@ -75,8 +75,8 @@
     <sheet name="PT.ASIA PALEM LESTARI (6)" sheetId="120" r:id="rId60"/>
     <sheet name="PT.ASIA PALEM LESTARI (7)" sheetId="121" r:id="rId61"/>
     <sheet name="PT.ASIA PALEM LESTARI (8)" sheetId="122" r:id="rId62"/>
-    <sheet name="PT.PERSADA GRAHA MANDIRI (1)" sheetId="18" r:id="rId63"/>
-    <sheet name="persada graha mandiri" sheetId="273" r:id="rId64"/>
+    <sheet name="persada graha mandiri" sheetId="273" r:id="rId63"/>
+    <sheet name="persada graha mandiri (1" sheetId="274" r:id="rId64"/>
     <sheet name="PT.PERSADA GRAHA MANDIRI (2)" sheetId="123" r:id="rId65"/>
     <sheet name="PT.PERSADA GRAHA MANDIRI (3)" sheetId="124" r:id="rId66"/>
     <sheet name="PT.PERSADA GRAHA MANDIRI (4)" sheetId="125" r:id="rId67"/>
@@ -62795,285 +62795,6 @@
 </file>
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3E00-000000000000}">
-  <sheetPr codeName="Sheet63"/>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="38.140625" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.85546875" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.5703125" customWidth="1"/>
-    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
-        <v>3130</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="C4" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="C5" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="C6" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="C7" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="C8" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="C9" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C10" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="C11" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="C12" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="C13" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="C14" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="C15" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="C16" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="C17" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C18" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="C19" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>45917</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="C21" s="12">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="C22" s="4">
-        <v>45552</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3829844-310B-45C4-96A1-1E604175A2DD}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -63158,6 +62879,256 @@
         <v>573</v>
       </c>
       <c r="C8" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1A31C7-7985-4C2D-A381-41D3FA6DA48A}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="121" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C4" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C5" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C6" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C7" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="C9" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C10" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C11" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C12" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C13" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C14" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C15" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C16" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C17" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C18" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C19" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="4">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>45917</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C21" s="12">
+        <v>45552</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>45917</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C22" s="4">
         <v>45552</v>
       </c>
     </row>
